--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q191"/>
+  <dimension ref="A1:Q194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13333,6 +13333,213 @@
         </is>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Category Manager - Wild Lama</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Wild Lama</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56853/category-manager-wild-lama</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>1</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>Rol : Category Manager Wild LamaReporte: Product ManagerLugar: Santiago, CL.Qué es lo que harásContribuir al logro de los objetivos definidos para el negocio, cumpliendo con los márgenes y crecimientos de las líneas y apoyando a los Product Manager.Apoyo en todo el proceso de compra: cotización, negociación, envío de órdenes de compra, creación de productos y seguimiento del desarrollo de los productos.Contacto directo con proveedores para los detalles del producto y seguimiento de la compra.Apoyar en el análisis de venta de productos, seguimiento de los resultados, definición de precios y continuo contacto con todos nuestros canales de venta.Constante comunicación con las distintas áreas involucradas en el proceso del producto: marketing, planificación, COMEX, etc.Quién eres:Una persona conPensamientoAnalítico,que identifique problemas, los entienda y los solucione.Una personaOrdenada, que tenga un trabajo metódico y sea capaz de prioriozar y gestionar sus tareas.Con muchaIniciativa. Oportunidades hay infinitas, sólo necesitamos que te atrevas.AltamenteAutónoma. En Wild Brands confiamos en el motor propio de cada miembro de nuestra organización.No estarás sol@. Te integrarás a un equipazo donde laColaboración y el Trabajo en Equipoes fundamental.Experiencia que traes:Título en Ingeniería Civil, Ingeniería Comercial o carrera afín.Entre 0 a 2 años de experiencia.En Wild Lama valoramos la diversidad, la equidad y la inclusión, que nos permiten contar con talentos que enriquecen el clima al interior de la empresa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Ingenieroa de Control de Gestión – Control Operacional</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>AFP Modelo</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Avda de valle 614 Huechuraba, Chile</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56851/ingeniero-a-de-control-de-gestion-control-operacional</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>8</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>python, sql, informatica</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>1</v>
+      </c>
+      <c r="L193" t="n">
+        <v>1</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>Gerencia de Operaciones🎯 Tu propósitoPromover la eficiencia y transparencia en los procesos ejecutados por el área de Operaciones, resguardando los recursos y bienes de los afiliados mediante el cumplimiento normativo.Además, serás responsable de asegurar el adecuado funcionamiento y nexo entre las áreas de Operaciones, CRA y Finanzas, contribuyendo al correcto y oportuno procesamiento de los movimientos contables.También participarás y serás promotor/a de iniciativas de mejora y simplificación de tareas administrativas y manuales, así como de otras acciones que contribuyan a optimizar los procesos del área.📚 FormaciónIngeniería Comercial.Ingeniería Civil Industrial.Ingeniería Civil Informática.Ingeniería en Informática.Ingeniería en Ejecución.Contador/a Auditor/a.Otras carreras afines.💻 Conocimientos técnicos deseablesAFP Net.Microsoft Office.SQL.Power Automate.Power BI.Python.Otros conocimientos relacionados.🔎 ExperienciaMínimo 1 año de experiencia en cargos similares.BeneficiosBus de acercamiento.Día de cumpleaños libre.Jornada híbrida.Seguro de salud.¡Y muchos más!🚀 ¡Postula ahora y sé parte del equipo!</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Analista Jr de Control Interno y Gestión Integral de Riesgos</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Tanner</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56847/analista-jr-de-control-interno-y-gestion-integral-de-riesgos</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>9</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>python, modelo, analisis, power bi</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>1</v>
+      </c>
+      <c r="L194" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="P194" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>Buscamos incorporar a nuestro equipo deRiesgos No Financierosa una persona que quiera asumir un rol clave en el fortalecimiento de nuestra gestión integral de riesgos y modelo de control interno.Tu desafío será contribuir a la identificación, evaluación y monitoreo de riesgos, apoyando la efectividad de los controles y el seguimiento de modelos que permitan fortalecer la gestión y sostenibilidad de la organización.¿Cuáles serán tus principales desafíos?Identificar, evaluar y monitorear riesgos operacionales y no financieros.Elaborar y mantener matrices de riesgos y controles (RCSA).Coordinar y mantener actualizado el Modelo de Control Interno, realizando seguimiento a la eficacia y diseño de controles.Participar en la evaluación y testing de controles.Definir y monitorear Indicadores Clave de Riesgo (KRIs).Analizar eventos de riesgo, sus causas y planes de mitigación.Apoyar la gestión y seguimiento de modelos asociados a riesgos y controles.Elaborar información y reportes para comités, Alta Administración y Directorio.Trabajar transversalmente con distintas áreas, asesorándolas en materias de riesgos, procesos y controles.¿Qué buscamos?Profesionales deIngeniería Civil Industrial, Ingeniería en Control de Gestión o carrera afín, con:Al menos 1año de experienciaen áreas relacionadas con riesgos, control interno, auditoría, control de gestión, cumplimiento o similares.Experiencia enRiesgo No Financieroy/o Riesgo Operacional.Experiencia encontrol y seguimiento de modelos, procesos o controles.Deseable experiencia en elsector financiero.Conocimientos en metodologías deprocesos, riesgos y controles.Será un plus si además cuentas con conocimientos ennormativa CMF, Basilea III, ILAAP/IAPE, COSO o IFRS; herramientas comoPower BI; y nociones deSQL, Python, SAS, R o similares, junto con capacidades de análisis cuantitativo.¿Te interesa ser parte de este desafío?En Tanner buscamos personas que quieran aportar desde su experiencia, asumir nuevos desafíos y generar impacto en una organización en constante evolución.¡Postula y sé parte de Tanner!Beneficios- Seguro complementario de Salud- Bono vacaciones- Aguinaldo sept y dic- otros</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q194"/>
+  <dimension ref="A1:Q202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13540,6 +13540,550 @@
         </is>
       </c>
     </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Sales Development Representative SDR</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Importante Empresa</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56873/sales-development-representative-sdr</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="n">
+        <v>1</v>
+      </c>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>El rolBuscamos un SDR que quiera crecer rápido, aprender mucho, y tener impacto real desde el primer mes. No es un rol de call center. Es un rol donde tú eres dueño de tu pipeline, tus métricas, y tus resultados de cierre.Algunas de tus funcionesCaptar y calificar leads a través de WhatsApp CRM, videollamadas y emailCerrar acuerdos en videollamada con dueños de propiedades premiumHacer seguimiento riguroso de tu funnel, cada lead, cada etapa, cada conversiónCoordinar con el equipo de operaciones para asegurar que las propiedades que cierras arrancan impecablesLo que buscamosCarrera afín: Ingeniería Comercial, Administración, Economía o similarExperiencia en ventas B2C o roles comerciales es un plus, no excluyenteHambre de aprender y crecerOrientación a resultadosBuena presencia en cámara y comunicación claraCompensaciónBase fija + comisiones por cierre.¿Por qué postular con nosotros?Porque en una empresa pequeña y de alto crecimiento aprendes más en seis meses que en tres años en una corporación. Vas a tener responsabilidad real, visibilidad directa.Si eres de las personas que prefieren hacer y no esperar, este es tu lugar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Business Development Senior Analyst</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Hanseatic Global Terminals Latin America</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Apoquindo 4800, Torre 2, Piso 9, Las Condes, Chile</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56872/business-development-senior-analyst</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>10</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>analisis, estadistica, trainee</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>1</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
+        <v>1</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
+        <v>1</v>
+      </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>¡Vive la experiencia de trabajar enHanseatic Global Terminals Latin America🤩!¿Quiénes somos?Somos la oficina regional de Hanseatic Global Terminals en América Latina. Líderes en servicios portuarios en el continente, contamos con 10 terminales portuarios al servicio del comercio exterior —Chile, Ecuador, Colombia, Costa Rica, México y Estados Unidos—, conectando industrias con Asia, Europa y América. Además, prestamos servicios logísticos integrales a importadores y exportadores 🚢🏗️.Como parte de la red global de Hanseatic Global Terminals (HGT), pertenecemos a un grupo con sede en Róterdam que gestiona una cartera de 22 terminales portuarios y servicios logísticos complementarios en 12 países y cinco continentes, centrada en la eficiencia, la seguridad y la sostenibilidad en apoyo de la logística mundial.Actualmente, nos encontramos en la búsqueda de unBusiness Development Senior Analyst😎 que cuente con gran capacidad de análisis, pueda expresar ideas de forma clara, atención al detalle, razonamiento lógico, orientado a resultados, capacidad de liderar y para trabajar en varios proyectos en simultáneo. Esta posición es parte de nuestro Programa Trainee, el cual busca el desarrollo acelerado de jóvenes con alto potencial profesional.💪 Funciones principalesInvestigar e identificar oportunidades de negocio e inversión apoyándose también con estudios de mercado.Analizar y proponer nuevas oportunidades de negocio presentando sus conclusiones y sugerencias.Gestionar las áreas que sean necesarias para la concreción de los proyectos aprobados por las jefaturas.Apoyo en procesos M&amp;A:  Due-Diligence, gestión de proyectos y proveedores.Preparación de modelos de valorización para procesos de M&amp;A o valorización de proyectos en licitaciones portuarias.🔎RequisitosIngeniero/a Civil Industrial o Ingeniero/a Comercial 🎓Contar con 1-2 años de experiencia en Evaluación de Proyectos o Valorización de Empresas.Inglés avanzado. 🌐Manejo avanzado de Excely herramientas ofimáticas. 💻Conocimientos en finanzas y estadística.Tener disponibilidad para trasladarse (por proyectos o por tiempo indefinido) dentro y fuera de Chile. ✈️✨ Plus para tu postulaciónMagister Financiero o Magister en Excelencia OperacionalExperiencia tipo en Equipos de Proyectos, Investment Banking, M&amp;APuntualidad y responsabilidad. ⏰Comunicación efectiva. 🗣️Residencia actual en la Región Metropolitana.✨ ¡Atrévete a ser parte de esta experiencia y potencia tu desarrollo profesional con nosotros! ✨BeneficiosSeguro de Vida.Vacunación contra la influenzaAguinaldos.Convenios.Reajustabilidad por IPC cuatrimestral.Reembolso de cursos que impulsen tu desarrollo profesional.Actividades extraprogramáticas frecuentes.BenefitsForYou: ¡Programa de Beneficios Flexible!</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Analista de Planificación – Food</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>KiosClub</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56868/analista-de-planificacion-food</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>6</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>python, analisis, matematica</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="P197" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>KiosClub American SupermarketSomos una empresa que surge en 2017 con el propósito de acercar productos internacionales al mercado chileno, con una propuesta diferenciada basada en marcas norteamericanas. Nuestro foco está en la variedad, la innovación y un servicio cercano.Hoy contamos con más de 50 tiendas a lo largo de todo el país y seguimos creciendo. Nuestra misión es ofrecer una experiencia de compra dinámica y entretenida, manteniendo estándares claros en nuestros productos y en la forma en que operamos.¡Estamos buscando a un/aAnalista de Planificación – Foodmotivado/a, analítico/a y con ganas de desarrollarse en una empresa dinámica y en constante crecimiento!Tus principales responsabilidades serán:Construir y actualizar elforecast de demanda de Foodpor categoría, subcategoría y SKU, incorporando historia de ventas, tendencias, estacionalidad, promociones, eventos comerciales, aperturas de tiendas, comportamiento por canal y productos nuevos.Medir la precisión y el sesgo del forecast, explicando desviaciones y ajustando los supuestos cuando sea necesario.Proyectar semanalmente elinventario, cobertura e in-stock, recomendando puntos de reorden, stock de seguridad y cantidades de reposición.Alertar anticipadamente riesgos dequiebre, sobrestock, vencimiento, merma y baja rotación.Elaborar recomendaciones de compra considerando demanda proyectada, inventario disponible y en tránsito, órdenes de compra abiertas, lead times, vencimientos y restricciones de caja y bodega.Desafiar con datos las cantidades propuestas por las áreas deCategory Management y Compras, aportando análisis para mejorar las decisiones de abastecimiento.Simular el impacto de promociones, descuentos, quiebres, eventos y cambios de precio sobre la demanda y el inventario.Preparar los insumos de Food para el ciclo deS&amp;OP, desarrollando escenarios de demanda, inventario y abastecimiento.Construir una proyección inicial de demanda sin restricciones y posteriormente modelar escenarios considerando restricciones de capital, capacidad de bodega y condiciones operacionales.Escalar oportunamente riesgos relevantes asociados aventas, margen, inventario, caja y capacidad operacional.Mantener modelos y tableros de planificación confiables, automatizados y auditables.Ejecutar controles de calidad sobre información de demanda, inventario, costos, productos, promociones e inventario en tránsito.Proponer mejoras a los modelos deforecast y reposición, buscando aumentar continuamente la precisión de la planificación.Requisitos:Titulado/a deIngeniería Civil Industrial, Ingeniería Comercial, Ingeniería Civil Matemática, Ingeniería en Información y Control de Gestióno carrera afín.Entre0 y 2 años de experienciaen planificación de demanda, Supply Chain, abastecimiento, control de gestión, Category Management o análisis comercial. Deseable experiencia en retail o consumo masivo.Manejo deExcel avanzado, excluyente.Deseable manejo deSQL, Python, Power Queryo herramientas de automatización.Conocimientos demargen, capital de trabajo, lead time, stock de seguridad, punto de reorden, nivel de servicio y GMROI.Capacidad para analizar información, trabajar con supuestos y desenvolverse con información incompleta.Capacidad para anticipar riesgos y transformar análisis de datos en recomendaciones para la toma de decisiones.BeneficiosAcceso a beneficios de Asociación Chilena de Seguridad y Caja Los Andes.Seguro de vida y salud complementario, vigente a partir de la contratación indefinida.Descuento de colaborador en productos de la marca.Beneficios de la plataforma BUK, incluyendo descuentos en servicios dentales, deportivos, vestuario, restaurantes, entre otros.Entrega de gift cards de la marca para compras en nuestras tiendas por Fiestas Patrias y Navidad, una vez alcanzada la contratación indefinida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Asistente Administrativo Servicios - Pasco</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Ferreyros</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Pasco, Perú</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56859/asistente-administrativo-servicios-pasco</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="n">
+        <v>1</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>Misión del puestoBrindar soporte administrativo y logístico al personal del equipo de servicios de la sucursal a fin de cumplir con los objetivos del área de acuerdo con las políticas y procedimientos establecidos por la Empresa.FuncionesElaborar las requisiciones y órdenes de compra, previamente autorizadas, generadas por los procesos desarrollados en el área de servicios.Realizar la recepción de facturas del área de servicios de la sucursal, generando las hojas de entrada y registrarlas a SAP para el pago a los proveedoresGestionar las órdenes de trabajo del área de servicios de la sucursal, desde la apertura, seguimiento, cierre y análisis de la rentabilidad de las OT´s próximas a facturación. Además, realizar la facturación de las OT´s desde la revisión de la documentación, el ingreso de la documentación al sistema (incluidas planillas de viajes) y solicitar y coordinar reapertura en caso se deba corregir la facturación. Finalmente, administrar y archivar facturas de las OT´s en files físicos.Emitir órdenes de pago y realizar la liquidación de gastos de viaje del personal técnico que realice trabajos en campo utilizando y actualizando la información en los sistemas, así como emitir vouchers de liquidación y tramitar su envío a Lima.Emitir reportes de sobretiempos para el personal técnico de Servicios y entregarlo para el trámite respectivo por medio del sistema respectivoVerificar la línea de crédito de los clientes y solicitar a Caja la confirmación de la autenticidad de los vouchers entregados por los clientes en coordinación con el área de Créditos y Cobranzas.Revisar el cierre contable y sus cuentas de gasto y de transferencia; así como elaborar y analizar los reportes de cuentas de gasto, de gerencias, ventas y rentabilidad de servicios y proyectos para el área; además, absolver las consultas sobre el cierre contable, cargos, etc.Realizar los informes que solicite la jefatura de Servicios analizando los indicadores de gestión del área.Girar notas de crédito de servicios realizados con la supervisión del jefe inmediatoControlar y solicitar el abastecimiento de suministros de útiles del área de Servicios.RequisitosEgresado(a) universitario de Ingeniería Industrial o carreras afines.Experiencia previa de 1 año desempeñando posiciones similares.Manejo de Office y SAP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Asistente De Planificación - Op. Antamina</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Ferreyros</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Ancash, Perú</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56858/asistente-de-planificacion-op-antamina</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>1</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>Misión del puestoGestionar la programación diaria de los trabajos mecánicos y preventivos de las flotas del cliente, garantizando el registro preciso en los sistemas de Ferreyros para optimizar la toma de decisiones en mina.FuncionesEnviar el programa diario de Mantenimiento Preventivo y backlogs a Ejecución; aperturar tareas por correctivos de turno y coordinar la parada de equipos y facilidades con el cliente (bahías, grúas, repuestos, soldadura).Actualizar y auditar en AMT el estatus de las OTs y pedidos. Cargar horómetros, tonelaje y metros perforados en AMT y el dispatch del cliente en SIGMA (vía SICA), asegurando la concordancia de datos entre ambas empresas.Preparar el paquete técnico completo para cada PM (Gantt, evaluaciones/tests de motor y frenos, backlogs firmados, hojas SOS, fichas de cambio de componentes y documentos de seguridad como PETS e IPERC).Reportar oportunamente incidentes y velar por el cumplimiento riguroso de las normas, instructivos y requisitos legales de SSMA de Ferreyros y la unidad minera.RequisitosEgresado(a) en Ingeniería Industrial, Administración, Mantenimiento de Maquinaria Pesada, Mecánica Automotriz o carreras afines.2 años de experiencia en funciones similares dentro del rubro minero o de maquinaria pesada.Conocimientos Clave en Planeamiento y programación de mantenimiento e Indicadores de gestión de mantenimiento (Disponibilidad, MTBF, MTTR, etc.).Disponibilida para trabajar  bajo régimen atípico en mina (Op. Antamina).</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Ingeniero Trainee - Lambayeque</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Ferreyros</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Lambayeque, Perú</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56857/ingeniero-trainee-lambayeque</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>13</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>trainee, excel, power bi, tableau</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" t="n">
+        <v>1</v>
+      </c>
+      <c r="M200" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" t="n">
+        <v>1</v>
+      </c>
+      <c r="O200" t="n">
+        <v>1</v>
+      </c>
+      <c r="P200" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>FuncionesGestión Operativa: Apertura de Órdenes de Trabajo (OT), programación del personal técnico y colocación de pedidos de repuestos necesarios.Supervisión Técnica: Acompañamiento en la supervisión de reparaciones, tanto en taller como en campo.Presupuestos y Servicio al Cliente: Elaboración de presupuestos de servicios para clientes internos y externos.Soporte Administrativo: Control y seguimiento de los procesos administrativos claves del área.RequisitosEgresado universitario de las carreras de Ingeniería Mecánica, Mecánica-Eléctrica e Industrial.1 año de experiencia laboral previa (se consideran prácticas preprofesionales y profesionales).Conocimientos comprobables en herramientas de visualización de datos y reportabilidad (Power BI, Tableau, Excel avanzado o similares).Disponibilidad total para laborar de forma presencial en la sucursal de Ferreyros en Lambayeque.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Analista de Exportaciones - Colina</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Rosen</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56862/analista-de-exportaciones-colina</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>2</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="n">
+        <v>1</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>📢 Si te gusta la decoración y el mundo del descanso familiar, ¡Rosenes para ti!  🚀Estamos buscando nuevos y nuevas RosenLovers que quieran ser parte de una de las mejores empresas para trabajar en Chile, rankingGPTW 2025.Buscamos el ADN Rosen en cada uno de nuestros/as colaboradores/as, potenciando la Excelencia, Integridad, Compromiso e Innovación.Actualmente nos encontramos en búsqueda de un/aAnalista de Exportacionesa trabajar en modalidad presencial en nuestro Centro de Distribución, ubicado en la comuna deColina, Región Metropolitana.📌¿Cuál es la misión de este rol?Asistir y administrar los procesos de despacho asociados al área de exportaciones (monitoreo de los portales web, ingreso de pedidos a SAP, emisión de facturas, evaluación de stock y control de la programación de despacho), para contribuir al cumplimiento de los requerimientos de la cartera de clientes asignados.📌¿Qué harás en este cargo?Monitorear los despachos de la cartera de clientes asignados, evaluando los niveles de stock, con la finalidad de cumplir con la programación diaria.Emitir facturas y rótulos de productos, con el objetivo de garantizar el recibo de la información, para la realización del proceso de despacho al cliente final.Procesar órdenes de pedidos, a través de portales específicos de la cartera de clientes, con la finalidad de exportar al sistema los requerimientos de los clientes finales. Adicionalmente, entregar resumen y documentación necesaria para satisfacción de los envíos a Despachador.Coordinar la programación, niveles de stock de los productos y documentación relevante(facturas anticipadas, bloqueo por crédito, anulación de facturas, u otros)para efectuar los despachos a Clientes finales.Responsable de asegurar y velar por el cumplimiento de la estrategia de sustentabilidad y sistema integrado de gestión en la empresa.Otros requerimientos propios del cargo.📌¿Cuáles son los requisitos para el rol?Título técnico o profesional de nivel superior en Comercio Exterior o Logística.Hasta 2 años de experiencia laboral en cargos vinculados a comercio exterior, operaciones logísticas, procesos de despacho y transporte.Manejo de Excel nivel intermedio.Disponibilidad para trabajar en modalidad presencial en nuestras oficinas en Colina, de lunes a viernes de 8:00 a 16:30 hrs.¡Te invitamos a ser parte de una compañía comprometida con sus colaboradores y la sustentabilidad! 🌱🙌En Rosen promovemos procesos de selección inclusivos y valoramos la diversidad. Si necesitas algún ajuste para participar, indícalo en tu postulación. Esta vacante se enmarca en nuestro compromiso con la inclusión laboral y la Ley 21.015.Beneficios🎁Beneficios:Bono de vacaciones 🏝Aguinaldos.30% de descuentos en Productos Rosen.Seguro Complementario de Salud (desde contrato indefinido).Día Libre de Cumpleaños 🎈Regalos Corporativos 🎁Buses de acercamientoCasino Corporativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>People Analyst Specialist</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Wherex</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56865/people-analyst-specialist</t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>11</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>python, sql, analisis, excel, looker</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="n">
+        <v>1</v>
+      </c>
+      <c r="L202" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>En wherex buscamos un/aPeople Analyst Specialistapasionado por los datos y la gestión del talento. En este rol, serás el puente entre el análisis estadístico y la estrategia de Recursos Humanos. Tu objetivo principal será transformar datos complejos en insights accionables para optimizar la toma de decisiones sobre nuestro equipo, mejorar la retención, acelerar la contratación y potenciar el compromiso de los colaboradores.¿Qué harás?Gestión de Datos:Recopilar, limpiar y estructurar datos de diferentes plataformas de Recursos Humanos (compensaciones, HRIS, ATS, evaluaciones de desempeño y encuestas).Creación de Dashboards:Diseñar y mantener tableros visuales interactivos (KPIs de rotación, tiempo de contratación, desempeño, etc.).Análisis Estadístico:Identificar patrones, correlaciones y tendencias en el comportamiento de los empleados para resolver problemas críticos del negocio.Modelos Predictivos:Desarrollar análisis avanzados para anticipar la fuga de talento y predecir necesidades futuras de contratación.Storytelling de Datos:Presentar informes claros y recomendaciones estratégicas a los líderes de la empresa y al equipo de RR.HH.Lo que buscamosEducación: Ingeniería Civil Industrial mención TI, Ingeniería en Computación; Ingeniería Comercial.Experiencia: hasta 2 años de experiencia en análisis de datos, preferiblemente aplicados al área de Recursos Humanos.Herramientas Técnicas: Dominio avanzado de Excel.Experiencia con herramientas de BI como Power BI, Looker.Manejo de SQL para la extracción de datos (Deseable).Conocimiento de Python o R (Altamente valorado).Fuerte pensamiento crítico, atención al detalle y excelente comunicación verbal y escrita.Este cargo es en Santiago de Chile (excluyente)Beneficios¿Por qué trabajar en Wherex?25 días de vacaciones al año (10 días adicionales a los días legales)Seguro Complementario (Médico/ Dental/ Vida)Aguinaldo Fiestas PatriasAguinaldo Fin de añoPago de dos días de licencia médica</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q176"/>
+  <dimension ref="A1:Q181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12342,6 +12342,351 @@
         </is>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Abogado(a) junior</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Forvis Mazars</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56973/abogado-a-junior</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>1</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>Con nosotros tienes la oportunidad de pertenecer a una firma internacional con un equipo de más de 40.000 profesionales altamente capacitados, que brinda servicios profesionales generando alto impacto en todos nuestros clientes en más de 100 países en los cinco continentes.Podrás formar parte de un equipo que valorará tus ideas, apoyará tus ambiciones y celebrará tus éxitos. En Forvis Mazars nos proponemos impulsar la colaboración y la flexibilidad, las diversas perspectivas de nuestros colaboradores y el progreso.Principales responsabilidades:· Revisar y redactar documentos legales relacionados con las labores del área.· Apoyar en la elaboración de contratos, informes, minutas y otros documentos jurídicos requeridos por clientes internos y externos.· Preparar informes, presentaciones y análisis jurídicos relativos a los distintos encargos.· Tramitación de causas judiciales ante Tribunales Tributarios y Aduaneros.· Apoyar procesos de Due Diligence, en materias corporativas, comerciales y/o laborales.· Colaborar en la gestión de múltiples encargos, asegurando el cumplimiento de los plazos y de los estándares de calidad.· Apoyar y gestionar trámites y requerimientos ante el SII, TGR y otros organismos públicos relacionados con las materias del área.Requisitos:· Abogada o abogado.· Experiencia de 0 a 2 años en estudios jurídicos, consultoras o en áreas legales corporativas.· Conocimientos en derecho corporativo, comercial y/o laboral.· Interés en desarrollarse profesionalmente en las áreas tributaria y corporativa.· Excelentes habilidades de redacción, análisis y comunicación.· Capacidad para trabajar bajo presión y gestionar múltiples proyectos simultáneamente.· Orientación al detalle y capacidad para analizar información compleja.· Inglés intermedio, oral y escrito.Ofrecemos:· Paquete de compensaciones de mercado.· Seguros complementarios de salud y dental, además de un seguro de vida.· Una experiencia dinámica, diversa e inclusiva, en una firma con orientación en las personas, el desarrollo y crecimiento.· Educación continua mediante programas internos, corporativos y externos.· Días adicionales de vacaciones.Este cargo es compatible para personas con discapacidad, se enmarca en la ley 21015, que incentiva la inclusión de personas con discapacidad al mundo laboral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Analista de Riesgo de Crédito y Analítica de Datos</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>BICE</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56977/analista-de-riesgo-de-credito-y-analitica-de-datos</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>9</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>python, sql, analisis, excel</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>1</v>
+      </c>
+      <c r="L178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>En Banco BICE creemos que las personas son el motor de nuestro crecimiento. Impulsamos el desarrollo profesional en un entorno colaborativo, desafiante y con sello humano, donde el aprendizaje continuo, la innovación y la excelencia son parte de nuestro día a día.¿Te interesa el análisis financiero, la gestión de riesgos y el uso de datos para apoyar la toma de decisiones?Estamos buscando un/aAnalista de Riesgo de Crédito y Analítica de Datospara sumarse a nuestra Gerencia de Riesgo Empresas. Buscamos personas con interés por combinar el análisis financiero tradicional con herramientas de datos, automatización e inteligencia artificial, contribuyendo al fortalecimiento de la gestión de riesgo del Banco.🔍 ¿Qué harás en este rol?✅ Analizar información financiera de empresas para la elaboración de informes de riesgo y evaluación crediticia.✅ Participar en el análisis y monitoreo de la cartera de clientes, aportando información para la toma de decisiones de riesgo.✅ Diseñar y desarrollar reportes, dashboards e indicadores que permitan visualizar la evolución y el comportamiento de la cartera.✅ Extraer, consolidar y analizar datos provenientes de distintas fuentes para generar información de gestión.✅ Participar en iniciativas de automatización y mejora continua de procesos del área.✅ Utilizar herramientas de analítica e inteligencia artificial para optimizar análisis, reportes y generación de información.✅ Colaborar con distintas áreas del Banco en proyectos relacionados con datos, tecnología y transformación digital.🎓 ¿Qué necesitas para postular?Título profesional de Ingeniería Comercial, Ingeniería Civil Industrial o carrera afín.Entre 0 y 3 años de experiencia laboral, idealmente en áreas financieras, riesgo, análisis de datos, inteligencia de negocios o similares.Interés en análisis financiero, evaluación de riesgo de empresas y gestión de datos.Manejo de Excel avanzado.Conocimientos de SQL.Deseable conocimiento de Python o herramientas de análisis de datos.Deseable interés o experiencia utilizando herramientas de inteligencia artificial aplicadas al análisis de información.Capacidad analítica, orientación al aprendizaje, proactividad y motivación por desarrollarse en un entorno desafiante.Si buscas desarrollarte en una posición donde podrás combinar finanzas, riesgo, tecnología y analítica de datos, aportando directamente a la toma de decisiones de una de las áreas estratégicas del Banco, este desafío es para ti.¡Te invitamos a postular y ser parte de Banco BICE!Beneficios🏢Modalidad de trabajo según rol:Algunas posiciones acceden a un sistema híbrido, mientras que las áreas comerciales operan 100% de forma presencial.🍽️Almuerzo diario cubierto:Si trabajas en casa matriz, accedes al casino corporativo con almuerzo gratuito. Si estás en una sucursal, se te asigna un monto diario para cubrir este gasto.🛍️Descuentos exclusivos y convenios:Acceso a beneficios con diversas empresas asociadas en áreas como salud, retail, entretenimiento y más.⚽Actividades internas:Participación en torneos deportivos, actividades lúdicas, operativos oftalmológicos y otras instancias que promueven el bienestar.🤝Cultura cercana y participativa:Ser parte activa de un entorno laboral colaborativo, donde se vive la cultura organizacional día a día.🩺Seguros complementarios:Cobertura en salud, dental y de vida, para que cuentes con mayor respaldo y tranquilidad.🐾Seguro para mascotas:Protección adicional para tus compañeros de cuatro patas.🏋️Convenio con gimnasios:Accede a tarifas preferenciales para mantenerte activo y saludable.🎓Formación continua:Convenios y descuentos con instituciones educativas para diplomados, cursos y otros programas de desarrollo profesional.🚲Acceso a bicicletero:Estacionamiento seguro para bicicletas en casa matriz.🅿️Convenio de estacionamientos:Tarifas preferenciales en estacionamientos cercanos.📱Convenio con Entel:Descuentos en planes y equipos móviles.🦷Red de centros odontológicos:Acceso a múltiples convenios para atención dental.🎁Bonos diversos:Incluye bonos por escolaridad, fallecimiento, vacaciones, invierno, excelencia académica, aguinaldos de Fiestas Patrias y Navidad, entre otros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Analista Precios de Transferencia</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Forvis Mazars</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56972/analista-precios-de-transferencia</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>3</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>analisis, excel</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>1</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>1</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Con nosotros tienes la oportunidad de pertenecer a una firma internacional con un equipo de más de 40.000 profesionales altamente capacitados, que brinda servicios profesionales generando alto impacto en todos nuestros clientes en más de 100 países en los cinco continentes.Podrás formar parte de un equipo que valorará tus ideas, apoyará tus ambiciones y celebrará tus éxitos. En Forvis Mazars nos proponemos impulsar la colaboración y la flexibilidad, las diversas perspectivas de nuestros colaboradores y el progreso.Responsabilidades Claves·Comprender y aplicar los conceptos definidos por la OCDE en materia de Precios de Transferencia.· Apoyar en la preparación de estudios e informes de Precios de Transferencia para clientes nacionales e internacionales.· Participar en la elaboración de análisis funcionales, identificando funciones, activos y riesgos de las compañías evaluadas.· Recopilar, revisar y analizar información financiera y operacional de los clientes.· Contribuir en la elaboración de documentación técnica y reportes requeridos por la normativa vigente.· Colaborar con el equipo en la ejecución de proyectos, asegurando el cumplimiento de plazos y estándares de calidad.Requisitos· Formación profesional en carreras como Ingeniería Comercial, Ingeniería Civil Industrial, Contador Auditor, Economía o carreras afines.· Experiencia entre 0 y 2 años en áreas de Precios de Transferencia, Impuestos, Auditoría o Finanzas.· Conocimientos básicos o interés en normativa de Precios de Transferencia y tributación internacional.· Manejo intermedio o avanzado de Excel y herramientas de análisis de datos.· Habilidades analíticas y capacidad para trabajar con grandes volúmenes de información.· Capacidad para analizar e interpretar información financiera y económica.· Excelentes habilidades de comunicación verbal y escrita.· Inglés intermedio o avanzado.Ofrecemos· Paquete de compensaciones de mercado· Seguro Complementarios de salud y dental, además de seguro de Vida· Una experiencia dinámica, diversa e inclusiva, en una Firma con orientación en las personas, desarrollo y crecimiento· Educación continua, tanto de programas internos, corporativos y externos· Clases grupales de para mejorar el idioma inglés.Este cargo es compatible para personas con discapacidad, se enmarca en la ley 21015, que incentiva la inclusión de personas con discapacidad al mundo laboral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Desarrollador Full Stack (IA &amp; Producto)</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Milimetrix</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56965/desarrollador-full-stack-ia-producto</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>10</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>analisis, informatica, cloud, aws, rag</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>1</v>
+      </c>
+      <c r="K180" t="n">
+        <v>1</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>EnMilimetrixsomos una consultora de e-commerce y marketing digital enfocada en resultados de negocio. Trabajamos con marcas referentes del mercado como The North Face, Patagonia, Victoria's Secret y O'Neill, entre otras.Estamos impulsando un área de desarrollo de software con el objetivo de potenciar nuestra herramienta interna de métricas, optimizando procesos de analítica y performance.El DesafíoBuscamos a la primera persona de nuestro equipo de desarrollo, con visión de producto y mentalidad analítica. Es un cargo con alta autonomía y en contacto directo con el negocio, para transformar sus necesidades en soluciones tecnológicas eficientes y sostenibles.Responsabilidades PrincipalesEvolución del producto:Diseñar, desarrollar e iterar la plataforma, desde la arquitectura hasta la interfaz.Integración de datos:Conectar APIs de plataformas como Google Ads, Meta Ads, GA4 y e-commerce, y construir los procesos que ordenan y transforman esa información.Funcionalidades con IA:Automatizar análisis, generar reportes y apoyar la toma de decisiones.Requisitos del PerfilFormación:Titulado en Ingeniería en Computación, Informática o carrera afín, o experiencia equivalente demostrable.Experiencia:1 a 2 años en desarrollo de software.Conocimientos TécnicosDesarrollo web:Experiencia sólida en al menos un framework moderno (ej. Next.js, Ruby on Rails, Django o equivalente).LLMs:Experiencia integrando modelos de lenguaje en aplicaciones (prompting, RAG, agentes).APIs:Consumo e integración de APIs REST de terceros.Herramientas de IA:Uso de IDEs con IA y agentes de código.Nube:Nociones de despliegue en AWS, Google Cloud o similares.DeseableConocimiento de marketing digital, e-commerce o métricas de campañas.Experiencia con herramientas de visualización o BI.BeneficiosAlgunos de los beneficios Milimetrix:Días libres por ocasión: Cumpleaños, mudanza, titulaciónFamilia: Licencias maternales y paternales extendidas (15 días adicionales). Los nuevos padres podrán trabajar de manera remota todas las tardes del primer medio año de vida de su nuevo integrante.Work from Anywhere: 3 semanas al año para trabajar 100% remoto; dos semanas son fijas (septiembre y Navidad/Año Nuevo) y una semana adicional es de libre elección.Vacaciones Premium: Si programas y te tomas 10 días de vacaciones consecutivos, ¡nosotros te regalamos un 11° día libre!Experiencia Milimetrix: actividades de equipo mensuales para fortalecer la colaboración y cultura interna.Make the dream: Después de cierto tiempo en la empresa, disfruta de hasta 6 meses sin goce de sueldo para perseguir ese sueño pendiente.Luna de miel prolongada: Añade 5 días extra a tu licencia matrimonial.Acompañamiento: Dos semanas libres en caso de pérdida de embarazo. Estamos contigo.Salud: Seguro complementario de salud y de vida sin costo.Convenio preferencial con MindFit Advanced, centro de entrenamiento ubicado en nuestro mismo edificio.Equipamiento: Macbook asignado por la compañía.Detalles de la posiciónUbicación: Las Condes, Santiago.Horario: Lun-Jue 09:00 - 18:15 hrs; Vie: 8:30-16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>📊 Paid Media Manager</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Milimetrix</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Callao 2911, Chile</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56185/paid-media-manager</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>2</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>1</v>
+      </c>
+      <c r="K181" t="n">
+        <v>1</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>¿Te motiva convertir datos en decisiones que disparen las ventas de marcas e-commerce?EnMilimetrix, agencia de performance creada por ex-ejecutivos retail &amp; e-commerce, buscamos a nuestro nuevoPaid Media Manager. Serás parte de un equipo que combina consultoría estratégica y ejecución hands-on para escalar negocios en toda Latam.No nos conformamos con ser una agencia común. Estamos impulsados por la excelencia y la innovación, buscando siempre nuevas formas de hacer crecer los negocios de nuestros clientes. Nuestra visión es convertirnos en la agencia líder en marketing digital de Latinoamérica, y sabemos que esto solo es posible trabajando con los mejores talentos del sector.Lo que harás día a díaAnálisis Ninja:Identificar y traducir métricas complejas en insights estratégicos de alto impacto para el negocio de nuestros clientes. Diagnosticar la salud de las campañas y proponer soluciones de optimización.Growth Hacker en formación:Lanzar, monitorear y optimizar campañas en Google Ads, Meta Ads y LinkedIn Ads para distintos objetivos (ventas, leads, awareness).Control de vuelo diario:Vigilar métricas clave, budgets y pacing; proponer ajustes pro-profit y test A/B.Storyteller de datos:Convertir KPIs en relatos claros para clientes y para el equipo, recomendando próximos pasos que generen impacto real.Lo que necesitas traerFormación:Recién egresada/o deIngeniería Comercial o Ingeniería Civil.ADN Milimetrix:Fuerte orientación a la excelencia y pasión por entender qué hace que un negocio crezca. Buscamos a alguien que aspire a la maestría técnica y estratégica en performance.Conocimientos:Preferentemente conocimientos básicos en Google Ads y Meta Ads (si tienes certificaciones, ¡mejor!). Si no los tienes, entrarás a la mejor empresa para aprender y crecer.Herramientas:Manejo intermedio de Excel/Sheets y pasión por los datos.Soft Skills:Proactividad, gestión del tiempo, comunicación clara y espíritu colaborativo.Lo que ganarásMentoría directa de especialistas top en performance y e-commerce.Plan de entrenamiento en atribución, CRO y AI tools (sí, jugamos con lo último).Ambiente start-up: rápido, meritocrático y con desafíos reales desde el día 1.BeneficiosAlgunos de los beneficios Milimetrix:Modalidad:Híbrida 3x2Días libres por ocasión:Cumpleaños, mudanza, titulaciónFamilia:Licencias maternales y paternales extendidas (15 días adicionales). Los nuevos padres podrán trabajar de manera remota todas las tardes del primer medio año de vida de su nuevo integrante.Work from Anywhere:3 semanas al año para trabajar 100% remoto; dos semanas son fijas (septiembre y Navidad/Año Nuevo) y una semana adicional es de libre elección.Vacaciones Premium:Si programas y te tomas 10 días de vacaciones consecutivos, ¡nosotros te regalamos un 11° día libre!Experiencia Milimetrix:actividades de equipo mensuales para fortalecer la colaboración y cultura interna.Make the dream:Después de cierto tiempo en la empresa, disfruta de hasta 6 meses sin goce de sueldo para perseguir ese sueño pendiente.Luna de miel prolongada:Añade 5 días extra a tu licencia matrimonial.Acompañamiento:Dos semanas libres en caso de pérdida de embarazo. Estamos contigo.Convenio preferencial con MindFit Advanced, centro de entrenamiento ubicado en nuestro mismo edificio.Salud:Seguro complementario de salud y de vida sin costo.Equipamiento:Macbook asignado por la compañía.Detalles del cargoUbicación:Las Condes, Santiago.Horario:Lun-Jue 09:00 - 18:15 hrs; Vie: 8:30 -16:30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q166"/>
+  <dimension ref="A1:Q173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11668,6 +11668,465 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Ejecutivo Comercial</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Wherex</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Nuevo León, México</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/57128/ejecutivo-comercial</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>1</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>¡En Wherex buscamos a nuestro/a próximo/a Ejecutivo/a de Operaciones Comerciales!Estarás a cargo de la gestión diaria de licitaciones que generan nuestros clientes y que son el corazón de nuestro negocio, para esto te apoyarás en nuestros sistemas con IA y de nuestra base de datos de más de 70 mil proveedores.¿Qué harás?Gestionar diariamente licitaciones asignadas por jefatura o área.Obtener las ofertas de los proveedores correctos, para aumentar la probabilidad de adjudicación de las licitaciones.Captar e inscribir nuevos proveedores, de acuerdo a los requerimientos solicitados.Identificar oportunidades en los procesos de la operación para proponer soluciones de mejora.Mantener información de la gestión realizada actualizada y ordenada en las diferentes herramientas de la compañía.¿Qué estamos buscando?Titulados de Administración de Empresas, Comercio Exterior, Negocios Internacionales o alguna carrera afín.1 a 2 años de experiencia.Interés por desarrollarte en el mundo de la atención al cliente.Ser una persona dinámica, orientada a los resultados y ordenada.Vivir en Monterrey (Aquí están nuestras oficinas).**Para completar tu postulación, no olvides realizar los test de Genomawork del link adjunto en esta publicación.¡Este es tu próximo desafío laboral!BeneficiosNuestros beneficios:25 días de vacaciones al año.Seguro gastos medicos mayores.Ambiente dinámico.Ambiente laboral de primera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Business Development Executive – Verken y Kaut</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Verken</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/57146/business-development-executive-verken-y-kaut</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Buscamos a una persona para impulsar el desarrollo comercial de nuestras dos marcas: convertir los leads que recibimos en ventas y abrir nuevas oportunidades de negocio a través de acuerdos comerciales y alianzas.Qué harásGestionar los leads de Verken y Kaut desde el primer contacto hasta el cierre.Negociar y cerrar acuerdos comerciales y alianzas con empresas, distribuidores y socios estratégicos.Diseñar y optimizar el viaje del cliente según el tipo de lead.Mantener el pipeline ordenado y reportar resultados.Qué buscamosIdealmente experiencia cerrando ventas y negociando acuerdos comerciales.Capacidad para relacionarse tanto con clientes finales como con empresas.Autonomía y orden para trabajar con métricas.Qué ofrecemosSueldo fijo más comisión por cierre.Un rol con impacto directo en el crecimiento de ambas marcas.Cargo con alto nivel de proyección y trabajo directo con socios.BeneficiosSeguro Complementario de Salud.Comisiones por cumplimiento de metas.Proyección en el cargo.Reportería directa a los dueños.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Analista de Contenido Junior</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Kitchen Center</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/57143/analista-de-contenido-junior</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>2</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>1</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
+        <v>1</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Kitchen Center imporante Empresa del rubro Retail, buscamos a una persona creativa, analítica y con gran interés en el mundo digital, para integrarse a un equipo de trabajo dinámico, donde podrá aportar a la generación de contenidos orientados al posicionamiento orgánico y crecimiento de visibilidad en canales digitales.Principales responsabilidades:Implementación y optimización de mejoras técnicas SEO para RRSS y sitio web.Redacción de textos SEO (blog, notas, descripciones de productos, recetas, comparativas, preguntas frecuentes, entre otros) implementando buenas prácticas del orgánico (html, H1, H2, estructura de textos).Elaboración semanal de un listado de palabras clave para orientar contenido estratégico y definir el calendario de contenido de SEO (según palabras clave y tendencias).Supervisión y actualización de las páginas web de las marcas, asegurando que el contenido esté vigente, alineado con campañas, correctamente vinculado y optimizado con palabras clave relevantes para mejorar su visibilidad.Medición del crecimiento del SEO tanto de Google como Social.Apoyo general en la planificación de RRSS (Redacción de copies para RRSS, CTA, considerando palabras clave relevantes, etc).Planificación y organización de contenido visual (fotos y vídeos) (considera hacer los Briefs para los videos)Apoyo transversal en la revisión y redacción de textos que se requieren en distintas áreas de la empresa.lacionadas con el desempeño del contenido orgánico.Perfil deseadoCarrera: Periodista.Experiencia: al menos 6 meses de experiencia comprobada en SEOBeneficiosTrabajo Híbrido 3x2Casino en Casa MatrizEstacionamientoGimnasio en Casa Matriz</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Líder de Branding, Dirección de Arte y Marketing Visual</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Verken</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Chesterton 7430, Las Condes, Chile</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/57126/lider-de-branding-direccion-de-arte-y-marketing-visual</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>En Verken &amp; Kaut estamos buscando una Líder de Branding, Dirección de Arte y Marketing Visual, apasionada por la construcción de marca y la dirección creativa, que nos ayude a seguir creciendo y posicionando nuestras marcas en el mercado.Funciones:Liderar la estrategia de branding global de ambas marcas.Definir y ejecutar la dirección de arte y los lineamientos visuales.Supervisar y desarrollar gráficas digitales para sitio web, redes sociales y campañas de ads.Diseñar y/o liderar el desarrollo de packaging, flyers y manuales de productos.Requisitos:Diseñadora (excluyente).Manejo avanzado de Photoshop e Illustrator (excluyente).2 años de experiencia en branding, dirección de arte o roles similares (ideal).Interés por liderar, proponer y hacer crecer el área visual.¿Qué esperamos de ti?Fuerte visión estratégica y creativa.Capacidad de liderar proyectos y proponer mejoras constantes.Autonomía, criterio y motor propio.Interés real por el crecimiento de marca y del equipo.BeneficiosSeguro Complementario</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Diseñador - Marca Outdoor &amp; Climatizacion</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Verken</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Chesterton 7430, Las Condes, Chile</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/57125/disenador-marca-outdoor-climatizacion</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" t="n">
+        <v>1</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>En Verken (climatización) &amp; Kaut (outdoor) seguimos creciendo y estamos buscando una apasionada del diseño  y  que nos ayude a seguir creciendo y posicionando nuestras marcas en el mercado.¿Qué funciones vas a tener?Estrategia de branding global de ambas marcasCrear gráficas digitales para la página web, redes sociales y ads.Diseño de packaging, flyers y manuales de productosImplementar grilla de contenidos en RRSS.Apoyar en la creación de contenido (sesiones, orgánico)Elaboración de campañas de Email marketing y flows.RequisitosEstudiaste diseño gráfico (excluyente).Muchas ganas de aprenderSaber usar Photoshop/Illustrator/Capcut avanzado (excluyente)2 años de experiencia¿Qué esperamos de ti?Tener ganas de aprenderSer crítica y proponer mejoras constantementeTener motor propio y proponer mejoras para tu áreaLiderar a equipo de practicantesLugar de Trabajo y modalidadLas Condes, presencialFull time</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Asistente Gestión y Desarrollo Op Mktplace</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Ripley chile</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Ofi Cerro Colorado 5240 - Internet, Chile</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/57107/asistente-gestion-y-desarrollo-op-mktplace</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>1</v>
+      </c>
+      <c r="L172" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>Asistente Gestión y Desarrollo Op MktplaceBeneficiosDescripción de los beneficios de la vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>vendedora</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>IGreen+</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/57130/vendedor-a</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L173" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>¡Es una oportunidad emocionante para incorporarte a iGreen Plus Solution Spa., empresa líder en soluciones de recarga para vehículos eléctricos (VE), como Vendedor/a! En este puesto, serás responsable de impulsar las ventas y la expansión de nuestra cartera de clientes en chile. Se trata de un puesto a tiempo completo en el que podrás contribuir a los objetivos comerciales de la empresa y desempeñar un papel clave en el dinámico sector de la movilidad eléctrica.El cargo consiste en promover y comercializar nuestras soluciones de recarga de vehículos eléctricos, captar nuevos clientes y mantener relaciones comerciales sólidas. Incluye la identificación de oportunidades de venta, la presentación de propuestas, el cierre de acuerdos y el seguimiento postventa, trabajando en estrecha coordinación con el equipo para garantizar la satisfacción del cliente y el crecimiento del negocio. Lo que harásIdentificar y contactar potenciales clientes (empresas, comercios, administraciones) para ofrecer soluciones de recarga de VEPresentar nuestros productos y servicios, explicando beneficios, características y opciones de inversiónElaborar presupuestos, propuestas comerciales y contratos adaptados a las necesidades de cada clienteNegociar condiciones y cerrar acuerdos de ventaRealizar seguimiento de la cartera de clientes existente, fomentando la fidelización y detectando oportunidades adicionalesMantenerse informado/a sobre novedades del sector, productos y tendencias del mercado en MalasiaReportar de forma periódica el avance de las ventas, los resultados y las acciones realizadas a la direcciónBeneficiosEn iGreen Plus Solution Spa. nos comprometemos a fomentar un entorno de trabajo dinámico y de apoyo que favorezca el crecimiento profesional. Ofrecemos remuneración competitiva + comisiones por ventas, prestaciones completas y vías de desarrollo profesional. Además, proporcionamos formación continua sobre productos, el sector y técnicas comerciales para que te mantengas a la vanguardia del cambiante mundo de la movilidad eléctrica. Te ofrecemos:💰 Remuneración competitiva + comisiones por ventas (atractivo esquema de incentivos ligado a resultados)📋 Prestaciones completas: seguro médico, cobertura hospitalaria y permisos según la legislación de Malasia📈 Plan de carrera y ascensos: vías claras de desarrollo profesional y formación continua🤝 Ambiente de trabajo: equipo joven y dinámico, cultura de innovación y apoyo mutuo🏖 Días de descanso: vacaciones anuales, permisos por enfermedad y ausencias especiales🧾 Reembolsos: gastos de desplazamiento y comunicaciones derivados de la actividad comercial¡Únete a nosotros y construye tu carrera en el sector del futuro!</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
